--- a/stories/arbres/ATOM-SEC.ADU.001-06.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Céline est à la serre. C'est la sortie de l'école. La maîtresse attend près de la porte. Maman est au rayon des pots. Papa doit les rejoindre. Céline a regardé les graines. Elle lève les yeux. Elle se souvient. On va vers papa. On va vers maman. On va vers la maîtresse. Céline marche vers les pots. Ses pieds restent près de maman. Ses mains tiennent le manteau de maman. Elle voit maman. Maman a le panier. Céline va vers maman. Maman dit : me voici. Tu vas vers papa, maman, ou la maîtresse. Céline est calme. L'air sent la terre humide.</t>
+          <t>Céline est à la serre. C'est la sortie de l'école. La maîtresse attend près de la porte. Maman est au rayon des pots. Papa doit les rejoindre. Céline a regardé les graines. Elle lève les yeux. Elle se souvient. On va vers papa. On va vers maman. On va vers la maîtresse. Céline marche vers les pots. Ses pieds restent près de maman. Ses mains tiennent le manteau de maman. Elle voit maman. Maman a le panier. Céline va vers maman. Me voici. Tu vas vers papa, maman, ou la maîtresse. Céline est calme. L'air sent la terre humide.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Céline est à la serre. C'est la sortie de l'école. La maîtresse attend près de la porte. Maman est au rayon des pots. Papa doit les rejoindre. Céline a regardé les graines. Elle lève les yeux. Elle se souvient. On va vers papa. On va vers maman. On va vers la maîtresse. Céline marche vers les pots. Ses pieds restent près de maman. Ses mains tiennent le manteau de maman. Elle voit maman. Maman a le panier. Céline va vers maman.
+maman|Me voici. Tu vas vers papa, maman, ou la maîtresse.
+narrateur|Céline est calme. L'air sent la terre humide.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Céline cherche quelqu'un. Vers qui va-t-elle ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Céline a cherché maman. Papa et la maîtresse sont aussi des adultes connus.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1840,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Céline tient le manteau de maman. Elles paient un petit pot.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2007,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2047,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.ADU.001-06.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.001-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Céline est calme. L'air sent la terre humide.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Céline cherche quelqu'un. Vers qui va-t-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1681,7 @@
           <t>narrateur|Céline a cherché maman. Papa et la maîtresse sont aussi des adultes connus.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1845,6 +1853,7 @@
           <t>narrateur|Céline tient le manteau de maman. Elles paient un petit pot.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2012,6 +2021,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2030,7 +2040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2054,6 +2064,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2255,6 +2279,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.ADU.001-06.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Céline va vers maman à la serre</t>
+          <t>La goutte et le pot de Mila</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une goutte glisse sur la vitre. Mila lève les yeux à la serre. Elle va vers maman, aux pots.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Céline est à la serre. C'est la sortie de l'école. La maîtresse attend près de la porte. Maman est au rayon des pots. Papa doit les rejoindre. Céline a regardé les graines. Elle lève les yeux. Elle se souvient. On va vers papa. On va vers maman. On va vers la maîtresse. Céline marche vers les pots. Ses pieds restent près de maman. Ses mains tiennent le manteau de maman. Elle voit maman. Maman a le panier. Céline va vers maman. Me voici. Tu vas vers papa, maman, ou la maîtresse. Céline est calme. L'air sent la terre humide.</t>
+          <t>Une goutte glisse sur la vitre de la serre. Elle laisse un trait brillant, tout fin. L'air sent la terre humide. Une arrosoir goutte encore, tout doux. Ploc. Ploc. La lumière est verte, à travers les feuilles. Un petit pot rouge attend sur la table. Mila vit avec papa et maman. C'est la sortie de l'école. En ce moment, Mila est à la serre. La maîtresse attend près de la porte. Maman est au rayon des pots. Papa doit les rejoindre. Mila a regardé les graines. Les sachets sont jaunes et verts. Elles sont toutes petites, les graines. Mila lève les yeux. Elle cherche. Maman ? Mila se souvient. On va vers papa. On va vers maman. On va vers la maîtresse. Je vais vers les pots. Mila marche vers les pots. Ses pieds restent près de la table. Ses mains tiennent le manteau de maman. Elle voit maman. Maman a le panier. Un pot rouge dépasse. Me voici, Mila. Je t'ai cherchée. Tu vas vers papa, maman, ou la maîtresse. Bravo. Tu es venue vers maman. La maîtresse est près de la porte. Oui. Papa arrive bientôt. Mila va vers maman. Parce qu'elle a cherché maman, elle la trouve. Le manteau est un peu humide, au bord. Ça sent la terre. Tu as fait du bon travail. On reste ensemble. Mila est calme. L'air sent encore la terre humide. La goutte finit sa course sur la vitre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,9 +1324,54 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Céline est à la serre. C'est la sortie de l'école. La maîtresse attend près de la porte. Maman est au rayon des pots. Papa doit les rejoindre. Céline a regardé les graines. Elle lève les yeux. Elle se souvient. On va vers papa. On va vers maman. On va vers la maîtresse. Céline marche vers les pots. Ses pieds restent près de maman. Ses mains tiennent le manteau de maman. Elle voit maman. Maman a le panier. Céline va vers maman.
-maman|Me voici. Tu vas vers papa, maman, ou la maîtresse.
-narrateur|Céline est calme. L'air sent la terre humide.</t>
+          <t>narrateur|Une goutte glisse sur la vitre de la serre.
+narrateur|Elle laisse un trait brillant, tout fin.
+narrateur|L'air sent la terre humide.
+narrateur|Une arrosoir goutte encore, tout doux.
+narrateur|Ploc.
+narrateur|Ploc.
+narrateur|La lumière est verte, à travers les feuilles.
+narrateur|Un petit pot rouge attend sur la table.
+narrateur|Mila vit avec papa et maman.
+narrateur|C'est la sortie de l'école.
+narrateur|En ce moment, Mila est à la serre.
+narrateur|La maîtresse attend près de la porte.
+narrateur|Maman est au rayon des pots.
+narrateur|Papa doit les rejoindre.
+narrateur|Mila a regardé les graines.
+narrateur|Les sachets sont jaunes et verts.
+enfant-f|Elles sont toutes petites, les graines.
+narrateur|Mila lève les yeux.
+narrateur|Elle cherche.
+enfant-f|Maman ?
+narrateur|Mila se souvient.
+narrateur|On va vers papa.
+narrateur|On va vers maman.
+narrateur|On va vers la maîtresse.
+enfant-f|Je vais vers les pots.
+narrateur|Mila marche vers les pots.
+narrateur|Ses pieds restent près de la table.
+narrateur|Ses mains tiennent le manteau de maman.
+narrateur|Elle voit maman.
+narrateur|Maman a le panier.
+narrateur|Un pot rouge dépasse.
+maman|Me voici, Mila.
+enfant-f|Je t'ai cherchée.
+maman|Tu vas vers papa, maman, ou la maîtresse.
+maman|Bravo.
+maman|Tu es venue vers maman.
+enfant-f|La maîtresse est près de la porte.
+maman|Oui.
+maman|Papa arrive bientôt.
+narrateur|Mila va vers maman.
+narrateur|Parce qu'elle a cherché maman, elle la trouve.
+narrateur|Le manteau est un peu humide, au bord.
+enfant-f|Ça sent la terre.
+maman|Tu as fait du bon travail.
+maman|On reste ensemble.
+narrateur|Mila est calme.
+narrateur|L'air sent encore la terre humide.
+narrateur|La goutte finit sa course sur la vitre.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1342,7 +1399,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Céline cherche quelqu'un. Vers qui va-t-elle ?</t>
+          <t>Mila cherche quelqu'un. Vers qui va-t-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1559,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Céline cherche quelqu'un. Vers qui va-t-elle ?</t>
+          <t>narrateur|Mila cherche quelqu'un.
+narrateur|Vers qui va-t-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1588,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Céline a cherché maman. Papa et la maîtresse sont aussi des adultes connus.</t>
+          <t>Mila a cherché maman. Elle est allée vers maman. Tu es venue vers moi ? Oui. Vers maman. Bravo, Mila. Papa et la maîtresse sont aussi des adultes connus. Mila tient encore le manteau. Le petit pot rouge est bien calé.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,7 +1736,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Céline a cherché maman. Papa et la maîtresse sont aussi des adultes connus.</t>
+          <t>narrateur|Mila a cherché maman.
+narrateur|Elle est allée vers maman.
+maman|Tu es venue vers moi ?
+enfant-f|Oui.
+enfant-f|Vers maman.
+maman|Bravo, Mila.
+maman|Papa et la maîtresse sont aussi des adultes connus.
+narrateur|Mila tient encore le manteau.
+narrateur|Le petit pot rouge est bien calé.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1706,7 +1772,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Céline tient le manteau de maman. Elles paient un petit pot.</t>
+          <t>Papa arrive près des pots. Me voici. Tu es avec maman ? Oui, papa. Bravo. Tu vas vers papa, maman, ou la maîtresse. Elles paient un petit pot. Mila tient le manteau de maman. Tu as fini, Mila ? Oui. Le pot est à nous. On le met près de la fenêtre, à la maison ? Oui. La terre dans le pot est douce et sombre.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1850,7 +1916,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Céline tient le manteau de maman. Elles paient un petit pot.</t>
+          <t>narrateur|Papa arrive près des pots.
+papa|Me voici.
+papa|Tu es avec maman ?
+enfant-f|Oui, papa.
+papa|Bravo.
+papa|Tu vas vers papa, maman, ou la maîtresse.
+narrateur|Elles paient un petit pot.
+narrateur|Mila tient le manteau de maman.
+maman|Tu as fini, Mila ?
+enfant-f|Oui.
+enfant-f|Le pot est à nous.
+papa|On le met près de la fenêtre, à la maison ?
+enfant-f|Oui.
+narrateur|La terre dans le pot est douce et sombre.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1878,7 +1957,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Je suis allée vers maman. Bravo. Tu as fait du bon travail. Le pot sent la terre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2018,7 +2097,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Je suis allée vers maman.
+papa|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Le pot sent la terre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2040,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2078,6 +2161,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.ADU.001-06.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.001-06.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une goutte glisse sur la vitre de la serre. Elle laisse un trait brillant, tout fin. L'air sent la terre humide. Une arrosoir goutte encore, tout doux. Ploc. Ploc. La lumière est verte, à travers les feuilles. Un petit pot rouge attend sur la table. Mila vit avec papa et maman. C'est la sortie de l'école. En ce moment, Mila est à la serre. La maîtresse attend près de la porte. Maman est au rayon des pots. Papa doit les rejoindre. Mila a regardé les graines. Les sachets sont jaunes et verts. Elles sont toutes petites, les graines. Mila lève les yeux. Elle cherche. Maman ? Mila se souvient. On va vers papa. On va vers maman. On va vers la maîtresse. Je vais vers les pots. Mila marche vers les pots. Ses pieds restent près de la table. Ses mains tiennent le manteau de maman. Elle voit maman. Maman a le panier. Un pot rouge dépasse. Me voici, Mila. Je t'ai cherchée. Tu vas vers papa, maman, ou la maîtresse. Bravo. Tu es venue vers maman. La maîtresse est près de la porte. Oui. Papa arrive bientôt. Mila va vers maman. Parce qu'elle a cherché maman, elle la trouve. Le manteau est un peu humide, au bord. Ça sent la terre. Tu as fait du bon travail. On reste ensemble. Mila est calme. L'air sent encore la terre humide. La goutte finit sa course sur la vitre.</t>
+          <t>Une goutte glisse sur la vitre de la serre. Elle laisse un trait brillant, tout fin. L'air sent la terre humide. Une arrosoir goutte encore, tout doux. Ploc. Ploc. La lumière est verte, à travers les feuilles. Un petit pot rouge attend sur la table. Mila vit avec papa et maman. C'est la sortie de l'école. En ce moment, Mila est à la serre. La maîtresse attend près de la porte. Maman est au rayon des pots. Papa doit les rejoindre. Mila a regardé les graines. Les sachets sont jaunes et verts. Elles sont toutes petites, les graines. Mila lève les yeux. Elle cherche. Maman ? Mila se souvient. On va vers papa. On va vers maman. On va vers la maîtresse. Je vais vers les pots. Mila marche vers les pots. Ses pieds restent près de la table. Ses mains tiennent le manteau de maman. Elle voit maman. Maman a le panier. Un pot rouge dépasse. Me voici, Mila. Je t'ai cherchée. Tu vas vers papa, maman, ou la maîtresse. Bravo. Tu es venue vers maman. La maîtresse est près de la porte. Oui. Papa arrive bientôt. Mila va vers maman. Parce qu'elle a cherché maman, elle la trouve. Le manteau est un peu humide, au bord. Ça sent la terre. On reste ensemble. Mila est calme. L'air sent encore la terre humide. La goutte finit sa course sur la vitre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Céline est à la serre. C'est la sortie de l'école. La maîtresse attend près de la porte. Maman est au rayon des pots. &lt;emphasis level="moderate"&gt;papa&lt;/emphasis&gt; doit les rejoindre. Céline a regardé les graines. Elle lève les yeux. Elle se souvient. On va vers papa. On va vers maman. On va vers la maîtresse. Céline marche vers les pots. Ses pieds restent près de maman. Ses mains tiennent le manteau de maman. Elle voit maman. Maman a le panier. Céline va vers maman. Maman dit : me voici. Tu vas vers papa, maman, ou la maîtresse. Céline est calme. L'air sent la terre humide.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une goutte glisse sur la vitre de la serre. Elle laisse un trait brillant, tout fin. L'air sent la terre humide. Une arrosoir goutte encore, tout doux. Ploc. Ploc. La lumière est verte, à travers les feuilles. Un petit pot rouge attend sur la table. Mila vit avec papa et maman. C'est la sortie de l'école. En ce moment, Mila est à la serre. La maîtresse attend près de la porte. Maman est au rayon des pots. Papa doit les rejoindre. Mila a regardé les graines. Les sachets sont jaunes et verts. Elles sont toutes petites, les graines. Mila lève les yeux. Elle cherche. Maman ? Mila se souvient. On va vers papa. On va vers maman. On va vers la maîtresse. Je vais vers les pots. Mila marche vers les pots. Ses pieds restent près de la table. Ses mains tiennent le manteau de maman. Elle voit maman. Maman a le panier. Un pot rouge dépasse. Me voici, Mila. Je t'ai cherchée. Tu vas vers papa, maman, ou la maîtresse. Bravo. Tu es venue vers maman. La maîtresse est près de la porte. Oui. Papa arrive bientôt. Mila va vers maman. Parce qu'elle a cherché maman, elle la trouve. Le manteau est un peu humide, au bord. Ça sent la terre. On reste ensemble. Mila est calme. L'air sent encore la terre humide. La goutte finit sa course sur la vitre.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1367,14 +1367,12 @@
 narrateur|Parce qu'elle a cherché maman, elle la trouve.
 narrateur|Le manteau est un peu humide, au bord.
 enfant-f|Ça sent la terre.
-maman|Tu as fait du bon travail.
 maman|On reste ensemble.
 narrateur|Mila est calme.
 narrateur|L'air sent encore la terre humide.
 narrateur|La goutte finit sa course sur la vitre.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1404,7 +1402,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Céline cherche quelqu'un. Vers qui va-t-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila cherche quelqu'un. Vers qui va-t-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1563,7 +1561,6 @@
 narrateur|Vers qui va-t-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1593,7 +1590,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Céline a cherché maman. &lt;emphasis level="moderate"&gt;papa&lt;/emphasis&gt; et la maîtresse sont aussi des adultes connus.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a cherché maman. Elle est allée vers maman. Tu es venue vers moi ? Oui. Vers maman. Bravo, Mila. Papa et la maîtresse sont aussi des adultes connus. Mila tient encore le manteau. Le petit pot rouge est bien calé.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1747,7 +1744,6 @@
 narrateur|Le petit pot rouge est bien calé.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1777,7 +1773,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Céline tient le manteau de &lt;emphasis level="moderate"&gt;maman&lt;/emphasis&gt;. Elles paient un petit pot.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa arrive près des pots. Me voici. Tu es avec maman ? Oui, papa. Bravo. Tu vas vers papa, maman, ou la maîtresse. Elles paient un petit pot. Mila tient le manteau de maman. Tu as fini, Mila ? Oui. Le pot est à nous. On le met près de la fenêtre, à la maison ? Oui. La terre dans le pot est douce et sombre.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1932,7 +1928,6 @@
 narrateur|La terre dans le pot est douce et sombre.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,12 +1952,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Je suis allée vers maman. Bravo. Tu as fait du bon travail. Le pot sent la terre. L'histoire est finie.</t>
+          <t>Je suis allée vers maman. Bravo. Le pot sent la terre.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je suis allée vers maman. Bravo. Le pot sent la terre.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2099,12 +2094,9 @@
         <is>
           <t>enfant-f|Je suis allée vers maman.
 papa|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|Le pot sent la terre.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le pot sent la terre.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2123,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2168,6 +2160,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.ADU.001-06.xlsx
+++ b/stories/arbres/ATOM-SEC.ADU.001-06.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>serre du jardin municipal</t>
+          <t>serre du jardin municipal, rayon des pots</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Céline, maman, papa, la maîtresse</t>
+          <t>Mila, maman, papa, la maîtresse</t>
         </is>
       </c>
     </row>
